--- a/eval/dataset/files/problems.xlsx
+++ b/eval/dataset/files/problems.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,12 +470,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48mA, 250 ohm</t>
+          <t>9V, 250 ohm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9V, 100 ohm</t>
+          <t>3V, 250 ohm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -500,12 +500,237 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24mA, 250 ohm</t>
+          <t>24V, 470 ohm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9V, 100 ohm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5V, 100 ohm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12V, 100 ohm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6V, 150 ohm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9V, 150 ohm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15V, 250 ohm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7.5V, 250 ohm</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4.5V, 100 ohm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10V, 470 ohm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.5V, 100 ohm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20V, 470 ohm</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.5V, 100 ohm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11V, 250 ohm</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8V, 150 ohm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13.5V, 470 ohm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -520,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.048A = 48mA</t>
+          <t>48.0mA</t>
         </is>
       </c>
     </row>
@@ -551,7 +776,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.024A = 24mA</t>
+          <t>24.0mA</t>
         </is>
       </c>
     </row>
@@ -561,7 +786,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>36.0mA</t>
         </is>
       </c>
     </row>
@@ -571,7 +796,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.09A = 90mA</t>
+          <t>12.0mA</t>
         </is>
       </c>
     </row>
@@ -581,7 +806,157 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6V</t>
+          <t>51.1mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>50.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>120.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>60.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>60.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>45.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21.3mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>42.6mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>44.0mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>53.3mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28.7mA</t>
         </is>
       </c>
     </row>
